--- a/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\15.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98DA988-7EDC-4E30-A71B-B37DA39A617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0E2B56-CB72-4F2E-95D4-FD145C3FBF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\15.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0E2B56-CB72-4F2E-95D4-FD145C3FBF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04910B87-CF95-41D4-932A-87796D574156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/15.05.2026 Макс ВБ/print_print_sorted.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\15.05.2026 Макс ВБ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\15.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0E2B56-CB72-4F2E-95D4-FD145C3FBF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E260CB14-6BD7-448F-86EF-B7D95DAB1E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -642,7 +653,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -665,11 +676,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -679,6 +701,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -981,11 +1004,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4210,7 +4235,14 @@
         <v>2</v>
       </c>
     </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E180" s="7">
+        <f>SUM(E2:E179)</f>
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>